--- a/04_DESIGN_TABLES/DesignTable_6802_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6802_SW2.xlsx
@@ -925,13 +925,13 @@
         <v>0.375</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -1162,13 +1162,13 @@
         <v>0.22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
@@ -1399,13 +1399,13 @@
         <v>0.28125</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
@@ -1636,13 +1636,13 @@
         <v>0.28125</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
@@ -1873,13 +1873,13 @@
         <v>0.375</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
@@ -2110,13 +2110,13 @@
         <v>0.375</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
@@ -2347,13 +2347,13 @@
         <v>0.44</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
@@ -2584,13 +2584,13 @@
         <v>0.44</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
@@ -2821,13 +2821,13 @@
         <v>0.44</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
@@ -3058,13 +3058,13 @@
         <v>0.53</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
@@ -3295,13 +3295,13 @@
         <v>0.53125</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
@@ -3532,13 +3532,13 @@
         <v>0.53125</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         <v>0.655</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
@@ -4006,13 +4006,13 @@
         <v>0.65625</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
@@ -4243,13 +4243,13 @@
         <v>0.65625</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
@@ -4480,13 +4480,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
@@ -4717,13 +4717,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
@@ -4954,13 +4954,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
@@ -5191,13 +5191,13 @@
         <v>0.9375</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.08253</v>
+        <v>1.08203</v>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>1.25</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.44338</v>
+        <v>1.44288</v>
       </c>
       <c r="BC21" t="inlineStr">
         <is>

--- a/04_DESIGN_TABLES/DesignTable_6802_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6802_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1245,86 +1245,86 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6802-06-04-NWO-FG</t>
+          <t>6802-04-06-NWO-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="C4" t="n">
-        <v>0.28125</v>
+        <v>0.28</v>
       </c>
       <c r="D4" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2252</v>
+        <v>0.2752</v>
       </c>
       <c r="F4" t="n">
-        <v>0.029</v>
+        <v>0.012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.285</v>
+        <v>0.349</v>
       </c>
       <c r="H4" t="n">
         <v>75</v>
       </c>
       <c r="I4" t="n">
-        <v>0.33332</v>
+        <v>0.40722</v>
       </c>
       <c r="J4" t="n">
         <v>75</v>
       </c>
       <c r="K4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="L4" t="n">
-        <v>0.285</v>
+        <v>0.349</v>
       </c>
       <c r="M4" t="n">
-        <v>0.325</v>
+        <v>0.397</v>
       </c>
       <c r="N4" t="n">
         <v>0.035</v>
       </c>
       <c r="O4" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0.182</v>
       </c>
-      <c r="P4" t="n">
-        <v>0.21875</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.28125</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.28125</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.2515</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.2405</v>
-      </c>
       <c r="Z4" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="AB4" t="n">
         <v>60</v>
@@ -1333,79 +1333,79 @@
         <v>37</v>
       </c>
       <c r="AD4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0.17</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.3</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AH4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AN4" t="n">
         <v>0.4375</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AO4" t="n">
         <v>0.05</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="AP4" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>0.02706</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AR4" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AS4" t="n">
         <v>0.05</v>
       </c>
-      <c r="AN4" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.2515</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.03007</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.01389</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0.05556</v>
-      </c>
       <c r="AT4" t="n">
-        <v>0.5625</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.5625</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.28125</v>
+        <v>0.28</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.28125</v>
+        <v>0.28</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.16188</v>
+        <v>0.16116</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.16188</v>
+        <v>0.16116</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.32426</v>
+        <v>0.32282</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
@@ -1413,34 +1413,34 @@
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.029</v>
+        <v>0.012</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.2252</v>
+        <v>0.2752</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0598</v>
+        <v>0.0738</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.01294730497827186</v>
+        <v>0.01560000198333998</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.22598</v>
+        <v>0.14998</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5593</v>
+        <v>0.5572</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>6802-06-04-NWO-FG</t>
+          <t>6802-04-06-NWO-FG</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 7/16-20 (adjustable male ORB) x 9/16-18 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 9/16-18 (adjustable male ORB) x 7/16-20 JIC</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>7/16-20 (adjustable male ORB)</t>
+          <t>9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
@@ -1465,79 +1465,79 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51528 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-CELL 2026-10-20: HEXB@HEX] JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51528 corroborates matched-dash); HEXB@HEX: Brennan TFA catalog p.41 table TFA-p041-t02 "MJ-MAORB 45 DEG ELBOW" row 6802-04-06-NWO-FG col "C HEX" = 0.688 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 0.56: a 0.56 locknut cannot fit the -06 ORB thread 9/16-18 (major 0.5625); generator BLOCKED ("Air-Way locknut hex 0.56 differs from the Brennan nut 0.6875 for -06"; the Brennan -06 locknut measured on the 6801 STEPs is 0.6875, catalog prints 0.688)) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>2026-10-20 HEXB@HEX = Brennan 0.688 (Air-Way 0.56 cannot be built: a 0.56 locknut cannot fit the -06 ORB thread 9/16-18 (major 0.5625); generator BLOCKED ("Air-Way locknut hex 0.56 differs from the Brennan nut 0.6875 for -06"; the Brennan -06 locknut measured on the 6801 STEPs is 0.6875, catalog prints 0.688)) | DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs)</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6802-06-04-NWO-FG</t>
+          <t>6802-04-06-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6802-06-06-NWO-FG</t>
+          <t>6802-06-04-NWO-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="C5" t="n">
         <v>0.28125</v>
       </c>
       <c r="D5" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2752</v>
+        <v>0.2252</v>
       </c>
       <c r="F5" t="n">
-        <v>0.012</v>
+        <v>0.029</v>
       </c>
       <c r="G5" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="H5" t="n">
         <v>75</v>
       </c>
       <c r="I5" t="n">
-        <v>0.40837</v>
+        <v>0.33332</v>
       </c>
       <c r="J5" t="n">
         <v>75</v>
       </c>
       <c r="K5" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="L5" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="M5" t="n">
-        <v>0.397</v>
+        <v>0.325</v>
       </c>
       <c r="N5" t="n">
         <v>0.035</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="P5" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.312</v>
+        <v>0.265</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="T5" t="n">
         <v>0.83</v>
@@ -1570,10 +1570,10 @@
         <v>37</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
         <v>0.3</v>
@@ -1582,22 +1582,22 @@
         <v>0.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.312</v>
+        <v>0.265</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AN5" t="n">
         <v>0.5625</v>
@@ -1621,7 +1621,7 @@
         <v>0.5625</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AV5" t="n">
         <v>0.5625</v>
@@ -1650,34 +1650,34 @@
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.012</v>
+        <v>0.029</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.2752</v>
+        <v>0.2252</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0598</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.01564019436220464</v>
+        <v>0.01294730497827186</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.15093</v>
+        <v>0.22598</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.5593</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>6802-06-06-NWO-FG</t>
+          <t>6802-06-04-NWO-FG</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 9/16-18 (adjustable male ORB) x 9/16-18 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 7/16-20 (adjustable male ORB) x 9/16-18 JIC</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>9/16-18 (adjustable male ORB)</t>
+          <t>7/16-20 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -1712,75 +1712,75 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6802-06-06-NWO-FG</t>
+          <t>6802-06-04-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6802-06-08-NWO-FG</t>
+          <t>6802-06-06-NWO-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="C6" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="D6" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="E6" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.35</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.445</v>
       </c>
       <c r="H6" t="n">
         <v>75</v>
       </c>
       <c r="I6" t="n">
-        <v>0.51807</v>
+        <v>0.40837</v>
       </c>
       <c r="J6" t="n">
         <v>75</v>
       </c>
       <c r="K6" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="L6" t="n">
-        <v>0.445</v>
+        <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.505</v>
+        <v>0.397</v>
       </c>
       <c r="N6" t="n">
-        <v>0.041</v>
+        <v>0.035</v>
       </c>
       <c r="O6" t="n">
-        <v>0.33</v>
+        <v>0.2405</v>
       </c>
       <c r="P6" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="R6" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="T6" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="U6" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="V6" t="n">
         <v>0.28125</v>
@@ -1807,34 +1807,34 @@
         <v>37</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
         <v>0.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AN6" t="n">
         <v>0.5625</v>
@@ -1855,31 +1855,31 @@
         <v>0.05556</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.314</v>
+        <v>0.274</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.21601</v>
+        <v>0.16188</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.21601</v>
+        <v>0.16188</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.43251</v>
+        <v>0.32426</v>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
@@ -1887,34 +1887,34 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.35</v>
+        <v>0.2752</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.095</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.01957904749094214</v>
+        <v>0.01564019436220464</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.19433</v>
+        <v>0.15093</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.7124</v>
+        <v>0.5593</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>6802-06-08-NWO-FG</t>
+          <t>6802-06-06-NWO-FG</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 3/4-16 (adjustable male ORB) x 9/16-18 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 9/16-18 (adjustable male ORB) x 9/16-18 JIC</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>3/4-16 (adjustable male ORB)</t>
+          <t>9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -1944,98 +1944,98 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.433) reaches 0.013 past the body face (0.420) inside the neck (max 0.105 off the axis vs neck radius 0.350) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6802-06-08-NWO-FG</t>
+          <t>6802-06-06-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6802-08-06-NWO-FG</t>
+          <t>6802-06-08-NWO-FG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="C7" t="n">
         <v>0.375</v>
       </c>
       <c r="D7" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2752</v>
+        <v>0.35</v>
       </c>
       <c r="F7" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="G7" t="n">
-        <v>0.35</v>
+        <v>0.445</v>
       </c>
       <c r="H7" t="n">
         <v>75</v>
       </c>
       <c r="I7" t="n">
-        <v>0.40837</v>
+        <v>0.51807</v>
       </c>
       <c r="J7" t="n">
         <v>75</v>
       </c>
       <c r="K7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="L7" t="n">
-        <v>0.35</v>
+        <v>0.445</v>
       </c>
       <c r="M7" t="n">
-        <v>0.397</v>
+        <v>0.505</v>
       </c>
       <c r="N7" t="n">
-        <v>0.035</v>
+        <v>0.041</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2405</v>
+        <v>0.33</v>
       </c>
       <c r="P7" t="n">
-        <v>0.28125</v>
+        <v>0.375</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.312</v>
+        <v>0.344</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="S7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="T7" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="U7" t="n">
         <v>0.375</v>
       </c>
       <c r="V7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="W7" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="AB7" t="n">
         <v>60</v>
@@ -2044,64 +2044,64 @@
         <v>37</v>
       </c>
       <c r="AD7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF7" t="n">
         <v>0.3</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.39</v>
-      </c>
       <c r="AG7" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="AH7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AN7" t="n">
         <v>0.5625</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AO7" t="n">
         <v>0.05556</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="AK7" t="n">
+      <c r="AP7" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>0.03007</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AR7" t="n">
         <v>0.01389</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AS7" t="n">
         <v>0.05556</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.2837</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.03383</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.01562</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.0625</v>
       </c>
       <c r="AT7" t="n">
         <v>0.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AV7" t="n">
         <v>0.75</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.323</v>
+        <v>0.314</v>
       </c>
       <c r="AX7" t="n">
         <v>0.375</v>
@@ -2124,34 +2124,34 @@
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.2752</v>
+        <v>0.35</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.095</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.01564019436220464</v>
+        <v>0.01957904749094214</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.30403</v>
+        <v>0.19433</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.7124</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>6802-08-06-NWO-FG</t>
+          <t>6802-06-08-NWO-FG</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 9/16-18 (adjustable male ORB) x 3/4-16 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 3/4-16 (adjustable male ORB) x 9/16-18 JIC</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>9/16-18 (adjustable male ORB)</t>
+          <t>3/4-16 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>3/4-16 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
@@ -2181,80 +2181,80 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.433) reaches 0.003 past the body face (0.430) inside the neck (max 0.051 off the axis vs neck radius 0.275) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.433) reaches 0.013 past the body face (0.420) inside the neck (max 0.105 off the axis vs neck radius 0.350) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6802-08-06-NWO-FG</t>
+          <t>6802-06-08-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6802-08-10-NWO-FG</t>
+          <t>6802-08-06-NWO-FG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>0.2752</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="G8" t="n">
-        <v>0.505</v>
+        <v>0.35</v>
       </c>
       <c r="H8" t="n">
         <v>75</v>
       </c>
       <c r="I8" t="n">
-        <v>0.58735</v>
+        <v>0.40837</v>
       </c>
       <c r="J8" t="n">
         <v>75</v>
       </c>
       <c r="K8" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="L8" t="n">
-        <v>0.505</v>
+        <v>0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5775</v>
+        <v>0.397</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3865</v>
+        <v>0.2405</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.391</v>
+        <v>0.312</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="T8" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="U8" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="V8" t="n">
         <v>0.375</v>
@@ -2281,34 +2281,34 @@
         <v>37</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
         <v>0.39</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.391</v>
+        <v>0.312</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AN8" t="n">
         <v>0.75</v>
@@ -2329,31 +2329,31 @@
         <v>0.0625</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.44</v>
+        <v>0.375</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.25353</v>
+        <v>0.21601</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.25353</v>
+        <v>0.21601</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.50757</v>
+        <v>0.43251</v>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
@@ -2361,34 +2361,34 @@
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.4</v>
+        <v>0.2752</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.105</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.02206561599670296</v>
+        <v>0.01564019436220464</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.23115</v>
+        <v>0.30403</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.8185</v>
+        <v>0.7124</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>6802-08-10-NWO-FG</t>
+          <t>6802-08-06-NWO-FG</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 7/8-14 (adjustable male ORB) x 3/4-16 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 9/16-18 (adjustable male ORB) x 3/4-16 JIC</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>7/8-14 (adjustable male ORB)</t>
+          <t>9/16-18 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -2418,95 +2418,95 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.508) reaches 0.008 past the body face (0.500) inside the neck (max 0.090 off the axis vs neck radius 0.400) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.433) reaches 0.003 past the body face (0.430) inside the neck (max 0.051 off the axis vs neck radius 0.275) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6802-08-10-NWO-FG</t>
+          <t>6802-08-06-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6802-10-08-NWO-FG</t>
+          <t>6802-08-10-NWO-FG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="C9" t="n">
         <v>0.44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0.019</v>
+        <v>0.03</v>
       </c>
       <c r="G9" t="n">
-        <v>0.445</v>
+        <v>0.505</v>
       </c>
       <c r="H9" t="n">
         <v>75</v>
       </c>
       <c r="I9" t="n">
-        <v>0.51807</v>
+        <v>0.58735</v>
       </c>
       <c r="J9" t="n">
         <v>75</v>
       </c>
       <c r="K9" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="L9" t="n">
-        <v>0.445</v>
+        <v>0.505</v>
       </c>
       <c r="M9" t="n">
-        <v>0.505</v>
+        <v>0.5775</v>
       </c>
       <c r="N9" t="n">
-        <v>0.041</v>
+        <v>0.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.33</v>
+        <v>0.3865</v>
       </c>
       <c r="P9" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.344</v>
+        <v>0.391</v>
       </c>
       <c r="R9" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="U9" t="n">
         <v>0.44</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="W9" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="AA9" t="n">
         <v>0.1546</v>
@@ -2518,64 +2518,64 @@
         <v>37</v>
       </c>
       <c r="AD9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.39</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.48</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="AH9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AN9" t="n">
         <v>0.75</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AO9" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="AK9" t="n">
+      <c r="AP9" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>0.03383</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AR9" t="n">
         <v>0.01562</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AS9" t="n">
         <v>0.0625</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.3553</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.03866</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.01786</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.07142999999999999</v>
       </c>
       <c r="AT9" t="n">
         <v>0.88</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="AV9" t="n">
         <v>0.88</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.352</v>
+        <v>0.333</v>
       </c>
       <c r="AX9" t="n">
         <v>0.44</v>
@@ -2598,34 +2598,34 @@
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.019</v>
+        <v>0.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.095</v>
+        <v>0.105</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.01957904749094214</v>
+        <v>0.02206561599670296</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.30043</v>
+        <v>0.23115</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.8185</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>6802-10-08-NWO-FG</t>
+          <t>6802-08-10-NWO-FG</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 3/4-16 (adjustable male ORB) x 7/8-14 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 7/8-14 (adjustable male ORB) x 3/4-16 JIC</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>3/4-16 (adjustable male ORB)</t>
+          <t>7/8-14 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
@@ -2655,74 +2655,74 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.508) reaches 0.028 past the body face (0.480) inside the neck (max 0.167 off the axis vs neck radius 0.350) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.508) reaches 0.008 past the body face (0.500) inside the neck (max 0.090 off the axis vs neck radius 0.400) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6802-10-08-NWO-FG</t>
+          <t>6802-08-10-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6802-10-10-NWO-FG</t>
+          <t>6802-10-08-NWO-FG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="C10" t="n">
         <v>0.44</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03</v>
+        <v>0.019</v>
       </c>
       <c r="G10" t="n">
-        <v>0.505</v>
+        <v>0.445</v>
       </c>
       <c r="H10" t="n">
         <v>75</v>
       </c>
       <c r="I10" t="n">
-        <v>0.58735</v>
+        <v>0.51807</v>
       </c>
       <c r="J10" t="n">
         <v>75</v>
       </c>
       <c r="K10" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="L10" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="M10" t="n">
         <v>0.505</v>
       </c>
-      <c r="M10" t="n">
-        <v>0.5775</v>
-      </c>
       <c r="N10" t="n">
-        <v>0.05</v>
+        <v>0.041</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3865</v>
+        <v>0.33</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="S10" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2755,10 +2755,10 @@
         <v>37</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
         <v>0.48</v>
@@ -2767,22 +2767,22 @@
         <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AN10" t="n">
         <v>0.875</v>
@@ -2806,7 +2806,7 @@
         <v>0.88</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="AV10" t="n">
         <v>0.88</v>
@@ -2835,34 +2835,34 @@
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.03</v>
+        <v>0.019</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.02206561599670296</v>
+        <v>0.01957904749094214</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.23115</v>
+        <v>0.30043</v>
       </c>
       <c r="BJ10" t="n">
         <v>0.8185</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>6802-10-10-NWO-FG</t>
+          <t>6802-10-08-NWO-FG</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 7/8-14 (adjustable male ORB) x 7/8-14 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 3/4-16 (adjustable male ORB) x 7/8-14 JIC</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>7/8-14 (adjustable male ORB)</t>
+          <t>3/4-16 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -2892,80 +2892,80 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.508) reaches 0.008 past the body face (0.500) inside the neck (max 0.090 off the axis vs neck radius 0.400) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.508) reaches 0.028 past the body face (0.480) inside the neck (max 0.167 off the axis vs neck radius 0.350) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6802-10-10-NWO-FG</t>
+          <t>6802-10-08-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6802-10-12-NWO-FG</t>
+          <t>6802-10-10-NWO-FG</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="C11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="D11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="G11" t="n">
-        <v>0.63</v>
+        <v>0.505</v>
       </c>
       <c r="H11" t="n">
         <v>75</v>
       </c>
       <c r="I11" t="n">
-        <v>0.73169</v>
+        <v>0.58735</v>
       </c>
       <c r="J11" t="n">
         <v>75</v>
       </c>
       <c r="K11" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="L11" t="n">
-        <v>0.63</v>
+        <v>0.505</v>
       </c>
       <c r="M11" t="n">
-        <v>0.722</v>
+        <v>0.5775</v>
       </c>
       <c r="N11" t="n">
         <v>0.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4725</v>
+        <v>0.3865</v>
       </c>
       <c r="P11" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="T11" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="V11" t="n">
         <v>0.4375</v>
@@ -2992,34 +2992,34 @@
         <v>37</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AF11" t="n">
         <v>0.48</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AN11" t="n">
         <v>0.875</v>
@@ -3040,31 +3040,31 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.402</v>
+        <v>0.352</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.3055</v>
+        <v>0.25353</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.3055</v>
+        <v>0.25353</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.61149</v>
+        <v>0.50757</v>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
@@ -3072,34 +3072,34 @@
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.13</v>
+        <v>0.105</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.02724775337832085</v>
+        <v>0.02206561599670296</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.23381</v>
+        <v>0.23115</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.9655</v>
+        <v>0.8185</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>6802-10-12-NWO-FG</t>
+          <t>6802-10-10-NWO-FG</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 1/16-12 (adjustable male ORB) x 7/8-14 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 7/8-14 (adjustable male ORB) x 7/8-14 JIC</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>1 1/16-12 (adjustable male ORB)</t>
+          <t>7/8-14 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -3129,98 +3129,98 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.612) reaches 0.042 past the body face (0.570) inside the neck (max 0.223 off the axis vs neck radius 0.500) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.508) reaches 0.008 past the body face (0.500) inside the neck (max 0.090 off the axis vs neck radius 0.400) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6802-10-12-NWO-FG</t>
+          <t>6802-10-10-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6802-12-10-NWO-FG</t>
+          <t>6802-10-12-NWO-FG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="C12" t="n">
-        <v>0.53125</v>
+        <v>0.53</v>
       </c>
       <c r="D12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="G12" t="n">
-        <v>0.505</v>
+        <v>0.63</v>
       </c>
       <c r="H12" t="n">
         <v>75</v>
       </c>
       <c r="I12" t="n">
-        <v>0.58735</v>
+        <v>0.73169</v>
       </c>
       <c r="J12" t="n">
         <v>75</v>
       </c>
       <c r="K12" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="L12" t="n">
-        <v>0.505</v>
+        <v>0.63</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5775</v>
+        <v>0.722</v>
       </c>
       <c r="N12" t="n">
         <v>0.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3865</v>
+        <v>0.4725</v>
       </c>
       <c r="P12" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V12" t="n">
         <v>0.4375</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.53125</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.53125</v>
-      </c>
       <c r="W12" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="AB12" t="n">
         <v>60</v>
@@ -3229,79 +3229,79 @@
         <v>37</v>
       </c>
       <c r="AD12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.48</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.61</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN12" t="n">
         <v>0.875</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AO12" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AP12" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>0.03866</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AR12" t="n">
         <v>0.01786</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AS12" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="AN12" t="n">
-        <v>1.0625</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.3895</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.04511</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.02083</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="AT12" t="n">
-        <v>1.0625</v>
+        <v>1.06</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.0625</v>
+        <v>1.06</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.416</v>
+        <v>0.402</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.53125</v>
+        <v>0.53</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.53125</v>
+        <v>0.53</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.30622</v>
+        <v>0.3055</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.30622</v>
+        <v>0.3055</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.61293</v>
+        <v>0.61149</v>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
@@ -3309,34 +3309,34 @@
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.105</v>
+        <v>0.13</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.02206561599670296</v>
+        <v>0.02724775337832085</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.38015</v>
+        <v>0.23381</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.9675</v>
+        <v>0.9655</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>6802-12-10-NWO-FG</t>
+          <t>6802-10-12-NWO-FG</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 7/8-14 (adjustable male ORB) x 1 1/16-12 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 1/16-12 (adjustable male ORB) x 7/8-14 JIC</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>7/8-14 (adjustable male ORB)</t>
+          <t>1 1/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
@@ -3366,74 +3366,74 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.613) reaches 0.063 past the body face (0.550) inside the neck (max 0.272 off the axis vs neck radius 0.400) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.612) reaches 0.042 past the body face (0.570) inside the neck (max 0.223 off the axis vs neck radius 0.500) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6802-12-10-NWO-FG</t>
+          <t>6802-10-12-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6802-12-12-NWO-FG</t>
+          <t>6802-12-10-NWO-FG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="C13" t="n">
         <v>0.53125</v>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F13" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="G13" t="n">
-        <v>0.63</v>
+        <v>0.505</v>
       </c>
       <c r="H13" t="n">
         <v>75</v>
       </c>
       <c r="I13" t="n">
-        <v>0.73169</v>
+        <v>0.58735</v>
       </c>
       <c r="J13" t="n">
         <v>75</v>
       </c>
       <c r="K13" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="L13" t="n">
-        <v>0.63</v>
+        <v>0.505</v>
       </c>
       <c r="M13" t="n">
-        <v>0.722</v>
+        <v>0.5775</v>
       </c>
       <c r="N13" t="n">
         <v>0.05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4725</v>
+        <v>0.3865</v>
       </c>
       <c r="P13" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="T13" t="n">
         <v>1.28</v>
@@ -3466,10 +3466,10 @@
         <v>37</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
         <v>0.61</v>
@@ -3478,22 +3478,22 @@
         <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AN13" t="n">
         <v>1.0625</v>
@@ -3517,7 +3517,7 @@
         <v>1.0625</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="AV13" t="n">
         <v>1.0625</v>
@@ -3546,34 +3546,34 @@
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.13</v>
+        <v>0.105</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.02724775337832085</v>
+        <v>0.02206561599670296</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.23581</v>
+        <v>0.38015</v>
       </c>
       <c r="BJ13" t="n">
         <v>0.9675</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
-          <t>6802-12-12-NWO-FG</t>
+          <t>6802-12-10-NWO-FG</t>
         </is>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 1/16-12 (adjustable male ORB) x 1 1/16-12 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 7/8-14 (adjustable male ORB) x 1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>1 1/16-12 (adjustable male ORB)</t>
+          <t>7/8-14 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -3603,44 +3603,44 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.613) reaches 0.043 past the body face (0.570) inside the neck (max 0.227 off the axis vs neck radius 0.500) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.613) reaches 0.063 past the body face (0.550) inside the neck (max 0.272 off the axis vs neck radius 0.400) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6802-12-12-NWO-FG</t>
+          <t>6802-12-10-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6802-12-16-NWO-FG</t>
+          <t>6802-12-12-NWO-FG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="C14" t="n">
-        <v>0.655</v>
+        <v>0.53125</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
         <v>0.027</v>
       </c>
       <c r="G14" t="n">
-        <v>0.755</v>
+        <v>0.63</v>
       </c>
       <c r="H14" t="n">
         <v>75</v>
       </c>
       <c r="I14" t="n">
-        <v>0.87603</v>
+        <v>0.73169</v>
       </c>
       <c r="J14" t="n">
         <v>75</v>
@@ -3649,34 +3649,34 @@
         <v>0.41</v>
       </c>
       <c r="L14" t="n">
-        <v>0.755</v>
+        <v>0.63</v>
       </c>
       <c r="M14" t="n">
-        <v>0.866</v>
+        <v>0.722</v>
       </c>
       <c r="N14" t="n">
         <v>0.05</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5975</v>
+        <v>0.4725</v>
       </c>
       <c r="P14" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="Q14" t="n">
         <v>0.469</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
         <v>0.41</v>
       </c>
       <c r="T14" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="U14" t="n">
-        <v>0.655</v>
+        <v>0.53125</v>
       </c>
       <c r="V14" t="n">
         <v>0.53125</v>
@@ -3703,19 +3703,19 @@
         <v>37</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
         <v>0.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AI14" t="n">
         <v>0.08333</v>
@@ -3751,31 +3751,31 @@
         <v>0.08333</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.31</v>
+        <v>1.0625</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.31</v>
+        <v>1.0625</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.556</v>
+        <v>0.416</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.655</v>
+        <v>0.53125</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.655</v>
+        <v>0.53125</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.37766</v>
+        <v>0.30622</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.37766</v>
+        <v>0.30622</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.75583</v>
+        <v>0.61293</v>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
@@ -3783,34 +3783,34 @@
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="BE14" t="n">
         <v>0.027</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.155</v>
+        <v>0.13</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.03242989075993877</v>
+        <v>0.02724775337832085</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.29357</v>
+        <v>0.23581</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.1696</v>
+        <v>0.9675</v>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
-          <t>6802-12-16-NWO-FG</t>
+          <t>6802-12-12-NWO-FG</t>
         </is>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 (adjustable male ORB) x 1 1/16-12 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 1/16-12 (adjustable male ORB) x 1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>1 5/16-12 (adjustable male ORB)</t>
+          <t>1 1/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -3835,49 +3835,49 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51528 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51528 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.756) reaches 0.056 past the body face (0.700) inside the neck (max 0.286 off the axis vs neck radius 0.600) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.613) reaches 0.043 past the body face (0.570) inside the neck (max 0.227 off the axis vs neck radius 0.500) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6802-12-16-NWO-FG</t>
+          <t>6802-12-12-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6802-16-12-NWO-FG</t>
+          <t>6802-12-16-NWO-FG</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1.86</v>
       </c>
       <c r="C15" t="n">
-        <v>0.65625</v>
+        <v>0.655</v>
       </c>
       <c r="D15" t="n">
         <v>0.7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F15" t="n">
         <v>0.027</v>
       </c>
       <c r="G15" t="n">
-        <v>0.63</v>
+        <v>0.755</v>
       </c>
       <c r="H15" t="n">
         <v>75</v>
       </c>
       <c r="I15" t="n">
-        <v>0.73169</v>
+        <v>0.87603</v>
       </c>
       <c r="J15" t="n">
         <v>75</v>
@@ -3886,52 +3886,52 @@
         <v>0.41</v>
       </c>
       <c r="L15" t="n">
-        <v>0.63</v>
+        <v>0.755</v>
       </c>
       <c r="M15" t="n">
-        <v>0.722</v>
+        <v>0.866</v>
       </c>
       <c r="N15" t="n">
         <v>0.05</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4725</v>
+        <v>0.5975</v>
       </c>
       <c r="P15" t="n">
-        <v>0.53125</v>
+        <v>0.65625</v>
       </c>
       <c r="Q15" t="n">
         <v>0.469</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
         <v>0.41</v>
       </c>
       <c r="T15" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="U15" t="n">
-        <v>0.65625</v>
+        <v>0.655</v>
       </c>
       <c r="V15" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="W15" t="n">
         <v>0.125</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="AB15" t="n">
         <v>60</v>
@@ -3940,19 +3940,19 @@
         <v>37</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="AE15" t="n">
         <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.0625</v>
+        <v>1.3125</v>
       </c>
       <c r="AI15" t="n">
         <v>0.08333</v>
@@ -3970,13 +3970,13 @@
         <v>0.08333</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AO15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.04511</v>
@@ -3988,31 +3988,31 @@
         <v>0.08333</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.3125</v>
+        <v>1.31</v>
       </c>
       <c r="AU15" t="n">
         <v>0.7</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.3125</v>
+        <v>1.31</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.65625</v>
+        <v>0.655</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.65625</v>
+        <v>0.655</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.37839</v>
+        <v>0.37766</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.37839</v>
+        <v>0.37766</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.75727</v>
+        <v>0.75583</v>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
@@ -4026,28 +4026,28 @@
         <v>0.027</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.13</v>
+        <v>0.155</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.02724775337832085</v>
+        <v>0.03242989075993877</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.44001</v>
+        <v>0.29357</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.1717</v>
+        <v>1.1696</v>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>6802-16-12-NWO-FG</t>
+          <t>6802-12-16-NWO-FG</t>
         </is>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 1/16-12 (adjustable male ORB) x 1 5/16-12 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 (adjustable male ORB) x 1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>1 1/16-12 (adjustable male ORB)</t>
+          <t>1 5/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
@@ -4072,24 +4072,24 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51528 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51528 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.758) reaches 0.058 past the body face (0.700) inside the neck (max 0.290 off the axis vs neck radius 0.500) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.756) reaches 0.056 past the body face (0.700) inside the neck (max 0.286 off the axis vs neck radius 0.600) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6802-16-12-NWO-FG</t>
+          <t>6802-12-16-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6802-16-16-NWO-FG</t>
+          <t>6802-16-12-NWO-FG</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -4102,19 +4102,19 @@
         <v>0.7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="n">
         <v>0.027</v>
       </c>
       <c r="G16" t="n">
-        <v>0.755</v>
+        <v>0.63</v>
       </c>
       <c r="H16" t="n">
         <v>75</v>
       </c>
       <c r="I16" t="n">
-        <v>0.87603</v>
+        <v>0.73169</v>
       </c>
       <c r="J16" t="n">
         <v>75</v>
@@ -4123,25 +4123,25 @@
         <v>0.41</v>
       </c>
       <c r="L16" t="n">
-        <v>0.755</v>
+        <v>0.63</v>
       </c>
       <c r="M16" t="n">
-        <v>0.866</v>
+        <v>0.722</v>
       </c>
       <c r="N16" t="n">
         <v>0.05</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5975</v>
+        <v>0.4725</v>
       </c>
       <c r="P16" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="Q16" t="n">
         <v>0.469</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
         <v>0.41</v>
@@ -4177,7 +4177,7 @@
         <v>37</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AE16" t="n">
         <v>1.86</v>
@@ -4189,7 +4189,7 @@
         <v>1.47</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AI16" t="n">
         <v>0.08333</v>
@@ -4263,28 +4263,28 @@
         <v>0.027</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.155</v>
+        <v>0.13</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.03242989075993877</v>
+        <v>0.02724775337832085</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.29567</v>
+        <v>0.44001</v>
       </c>
       <c r="BJ16" t="n">
         <v>1.1717</v>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
-          <t>6802-16-16-NWO-FG</t>
+          <t>6802-16-12-NWO-FG</t>
         </is>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 (adjustable male ORB) x 1 5/16-12 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 1/16-12 (adjustable male ORB) x 1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>1 5/16-12 (adjustable male ORB)</t>
+          <t>1 1/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -4309,49 +4309,49 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51528 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51528 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.758) reaches 0.058 past the body face (0.700) inside the neck (max 0.290 off the axis vs neck radius 0.600) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.758) reaches 0.058 past the body face (0.700) inside the neck (max 0.290 off the axis vs neck radius 0.500) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6802-16-16-NWO-FG</t>
+          <t>6802-16-12-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6802-16-20-NWO-FG</t>
+          <t>6802-16-16-NWO-FG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F17" t="n">
         <v>0.027</v>
       </c>
       <c r="G17" t="n">
-        <v>0.945</v>
+        <v>0.755</v>
       </c>
       <c r="H17" t="n">
         <v>75</v>
       </c>
       <c r="I17" t="n">
-        <v>1.09542</v>
+        <v>0.87603</v>
       </c>
       <c r="J17" t="n">
         <v>75</v>
@@ -4360,34 +4360,34 @@
         <v>0.41</v>
       </c>
       <c r="L17" t="n">
-        <v>0.945</v>
+        <v>0.755</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0825</v>
+        <v>0.866</v>
       </c>
       <c r="N17" t="n">
         <v>0.05</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="Q17" t="n">
         <v>0.469</v>
       </c>
       <c r="R17" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
         <v>0.41</v>
       </c>
       <c r="T17" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="V17" t="n">
         <v>0.65625</v>
@@ -4414,19 +4414,19 @@
         <v>37</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
         <v>0.84</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AI17" t="n">
         <v>0.08333</v>
@@ -4462,31 +4462,31 @@
         <v>0.08333</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.629</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.94058</v>
+        <v>0.75727</v>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
@@ -4494,34 +4494,34 @@
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="BE17" t="n">
         <v>0.027</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.195</v>
+        <v>0.155</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0403049175254895</v>
+        <v>0.03242989075993877</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.33548</v>
+        <v>0.29567</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.4309</v>
+        <v>1.1717</v>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>6802-16-20-NWO-FG</t>
+          <t>6802-16-16-NWO-FG</t>
         </is>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 (adjustable male ORB) x 1 5/16-12 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 (adjustable male ORB) x 1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>1 5/8-12 (adjustable male ORB)</t>
+          <t>1 5/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -4551,19 +4551,19 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.941) reaches 0.191 past the body face (0.750) inside the neck (max 0.568 off the axis vs neck radius 0.750) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.758) reaches 0.058 past the body face (0.700) inside the neck (max 0.290 off the axis vs neck radius 0.600) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6802-16-20-NWO-FG</t>
+          <t>6802-16-16-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6802-20-16-NWO-FG</t>
+          <t>6802-16-20-NWO-FG</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -4576,19 +4576,19 @@
         <v>0.75</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F18" t="n">
         <v>0.027</v>
       </c>
       <c r="G18" t="n">
-        <v>0.755</v>
+        <v>0.945</v>
       </c>
       <c r="H18" t="n">
         <v>75</v>
       </c>
       <c r="I18" t="n">
-        <v>0.87603</v>
+        <v>1.09542</v>
       </c>
       <c r="J18" t="n">
         <v>75</v>
@@ -4597,52 +4597,52 @@
         <v>0.41</v>
       </c>
       <c r="L18" t="n">
-        <v>0.755</v>
+        <v>0.945</v>
       </c>
       <c r="M18" t="n">
-        <v>0.866</v>
+        <v>1.0825</v>
       </c>
       <c r="N18" t="n">
         <v>0.05</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5975</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.65625</v>
+        <v>0.8125</v>
       </c>
       <c r="Q18" t="n">
         <v>0.469</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="S18" t="n">
         <v>0.41</v>
       </c>
       <c r="T18" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="U18" t="n">
         <v>0.8149999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="W18" t="n">
         <v>0.125</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="AB18" t="n">
         <v>60</v>
@@ -4651,19 +4651,19 @@
         <v>37</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AE18" t="n">
         <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3125</v>
+        <v>1.625</v>
       </c>
       <c r="AI18" t="n">
         <v>0.08333</v>
@@ -4681,13 +4681,13 @@
         <v>0.08333</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AO18" t="n">
         <v>0.08333</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.04511</v>
@@ -4708,7 +4708,7 @@
         <v>1.63</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.632</v>
+        <v>0.629</v>
       </c>
       <c r="AX18" t="n">
         <v>0.8149999999999999</v>
@@ -4737,28 +4737,28 @@
         <v>0.027</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.155</v>
+        <v>0.195</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.03242989075993877</v>
+        <v>0.0403049175254895</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.55487</v>
+        <v>0.33548</v>
       </c>
       <c r="BJ18" t="n">
         <v>1.4309</v>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>6802-20-16-NWO-FG</t>
+          <t>6802-16-20-NWO-FG</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 (adjustable male ORB) x 1 5/8-12 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 (adjustable male ORB) x 1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>1 5/16-12 (adjustable male ORB)</t>
+          <t>1 5/8-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
@@ -4788,19 +4788,19 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.941) reaches 0.191 past the body face (0.750) inside the neck (max 0.568 off the axis vs neck radius 0.600) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.941) reaches 0.191 past the body face (0.750) inside the neck (max 0.568 off the axis vs neck radius 0.750) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6802-20-16-NWO-FG</t>
+          <t>6802-16-20-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6802-20-20-NWO-FG</t>
+          <t>6802-20-16-NWO-FG</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -4813,19 +4813,19 @@
         <v>0.75</v>
       </c>
       <c r="E19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F19" t="n">
         <v>0.027</v>
       </c>
       <c r="G19" t="n">
-        <v>0.945</v>
+        <v>0.755</v>
       </c>
       <c r="H19" t="n">
         <v>75</v>
       </c>
       <c r="I19" t="n">
-        <v>1.09542</v>
+        <v>0.87603</v>
       </c>
       <c r="J19" t="n">
         <v>75</v>
@@ -4834,25 +4834,25 @@
         <v>0.41</v>
       </c>
       <c r="L19" t="n">
-        <v>0.945</v>
+        <v>0.755</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0825</v>
+        <v>0.866</v>
       </c>
       <c r="N19" t="n">
         <v>0.05</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="Q19" t="n">
         <v>0.469</v>
       </c>
       <c r="R19" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
         <v>0.41</v>
@@ -4888,7 +4888,7 @@
         <v>37</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AE19" t="n">
         <v>1.91</v>
@@ -4900,7 +4900,7 @@
         <v>1.59</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AI19" t="n">
         <v>0.08333</v>
@@ -4974,28 +4974,28 @@
         <v>0.027</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.195</v>
+        <v>0.155</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.0403049175254895</v>
+        <v>0.03242989075993877</v>
       </c>
       <c r="BI19" t="n">
-        <v>0.33548</v>
+        <v>0.55487</v>
       </c>
       <c r="BJ19" t="n">
         <v>1.4309</v>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
-          <t>6802-20-20-NWO-FG</t>
+          <t>6802-20-16-NWO-FG</t>
         </is>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 (adjustable male ORB) x 1 5/8-12 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 (adjustable male ORB) x 1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>1 5/8-12 (adjustable male ORB)</t>
+          <t>1 5/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
@@ -5025,44 +5025,44 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.941) reaches 0.191 past the body face (0.750) inside the neck (max 0.568 off the axis vs neck radius 0.750) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.941) reaches 0.191 past the body face (0.750) inside the neck (max 0.568 off the axis vs neck radius 0.600) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6802-20-20-NWO-FG</t>
+          <t>6802-20-16-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6802-24-24-NWO-FG</t>
+          <t>6802-20-20-NWO-FG</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1.91</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D20" t="n">
         <v>0.75</v>
       </c>
       <c r="E20" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F20" t="n">
         <v>0.027</v>
       </c>
       <c r="G20" t="n">
-        <v>1.07</v>
+        <v>0.945</v>
       </c>
       <c r="H20" t="n">
         <v>75</v>
       </c>
       <c r="I20" t="n">
-        <v>1.23976</v>
+        <v>1.09542</v>
       </c>
       <c r="J20" t="n">
         <v>75</v>
@@ -5071,52 +5071,52 @@
         <v>0.41</v>
       </c>
       <c r="L20" t="n">
-        <v>1.07</v>
+        <v>0.945</v>
       </c>
       <c r="M20" t="n">
-        <v>1.227</v>
+        <v>1.0825</v>
       </c>
       <c r="N20" t="n">
         <v>0.05</v>
       </c>
       <c r="O20" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="Q20" t="n">
         <v>0.469</v>
       </c>
       <c r="R20" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="S20" t="n">
         <v>0.41</v>
       </c>
       <c r="T20" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="W20" t="n">
         <v>0.125</v>
       </c>
       <c r="X20" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="AB20" t="n">
         <v>60</v>
@@ -5125,19 +5125,19 @@
         <v>37</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AE20" t="n">
         <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="AI20" t="n">
         <v>0.08333</v>
@@ -5155,13 +5155,13 @@
         <v>0.08333</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="AO20" t="n">
         <v>0.08333</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.04511</v>
@@ -5173,31 +5173,31 @@
         <v>0.08333</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.875</v>
+        <v>1.63</v>
       </c>
       <c r="AU20" t="n">
         <v>0.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.875</v>
+        <v>1.63</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.697</v>
+        <v>0.632</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.9375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.9375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.54077</v>
+        <v>0.47004</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.54077</v>
+        <v>0.47004</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.08203</v>
+        <v>0.94058</v>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
@@ -5211,28 +5211,28 @@
         <v>0.027</v>
       </c>
       <c r="BF20" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.22</v>
+        <v>0.195</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.04548705490710737</v>
+        <v>0.0403049175254895</v>
       </c>
       <c r="BI20" t="n">
-        <v>0.39114</v>
+        <v>0.33548</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1.6309</v>
+        <v>1.4309</v>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
-          <t>6802-24-24-NWO-FG</t>
+          <t>6802-20-20-NWO-FG</t>
         </is>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 7/8-12 (adjustable male ORB) x 1 7/8-12 JIC</t>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 (adjustable male ORB) x 1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>1 7/8-12 (adjustable male ORB)</t>
+          <t>1 5/8-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>1 7/8-12 JIC</t>
+          <t>1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
@@ -5262,44 +5262,44 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.87 to 1.8750 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 1.083) reaches 0.333 past the body face (0.750) inside the neck (max 0.781 off the axis vs neck radius 0.850) - as on the 45 deg Brennan forgings</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 1: the corner puck (radius 0.941) reaches 0.191 past the body face (0.750) inside the neck (max 0.568 off the axis vs neck radius 0.750) - as on the 45 deg Brennan forgings</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6802-24-24-NWO-FG</t>
+          <t>6802-20-20-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6802-32-32-NWO-FG</t>
+          <t>6802-24-24-NWO-FG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="C21" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="D21" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="F21" t="n">
         <v>0.027</v>
       </c>
       <c r="G21" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="H21" t="n">
         <v>75</v>
       </c>
       <c r="I21" t="n">
-        <v>1.59771</v>
+        <v>1.23976</v>
       </c>
       <c r="J21" t="n">
         <v>75</v>
@@ -5308,52 +5308,52 @@
         <v>0.41</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="M21" t="n">
-        <v>1.58</v>
+        <v>1.227</v>
       </c>
       <c r="N21" t="n">
         <v>0.05</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1905</v>
+        <v>0.878</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="Q21" t="n">
         <v>0.469</v>
       </c>
       <c r="R21" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="S21" t="n">
         <v>0.41</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="W21" t="n">
         <v>0.125</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="AB21" t="n">
         <v>60</v>
@@ -5362,19 +5362,19 @@
         <v>37</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.781</v>
+        <v>1.31</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.781</v>
+        <v>1.31</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="AI21" t="n">
         <v>0.08333</v>
@@ -5392,13 +5392,13 @@
         <v>0.08333</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="AO21" t="n">
         <v>0.08333</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.04511</v>
@@ -5410,99 +5410,336 @@
         <v>0.08333</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.887</v>
+        <v>0.697</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.72119</v>
+        <v>0.54077</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.72119</v>
+        <v>0.54077</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.44288</v>
+        <v>1.08203</v>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="BE21" t="n">
         <v>0.027</v>
       </c>
       <c r="BF21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0.04548705490710737</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1.6309</v>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>6802-24-24-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>45 deg Male JIC x Adjustable Male ORB Elbow, 1 7/8-12 (adjustable male ORB) x 1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>6802</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51528 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.87 to 1.8750 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 1.083) reaches 0.333 past the body face (0.750) inside the neck (max 0.781 off the axis vs neck radius 0.850) - as on the 45 deg Brennan forgings</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>6802-24-24-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6802-32-32-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E22" t="n">
         <v>1.1</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="F22" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H22" t="n">
+        <v>75</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.59771</v>
+      </c>
+      <c r="J22" t="n">
+        <v>75</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>37</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.44288</v>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG22" t="n">
         <v>0.28</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BH22" t="n">
         <v>0.05833521868417974</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BI22" t="n">
         <v>0.54349</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BJ22" t="n">
         <v>2.1412</v>
       </c>
-      <c r="BK21" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>6802-32-32-NWO-FG</t>
         </is>
       </c>
-      <c r="BL21" t="inlineStr">
+      <c r="BL22" t="inlineStr">
         <is>
           <t>45 deg Male JIC x Adjustable Male ORB Elbow, 2 1/2-12 (adjustable male ORB) x 2 1/2-12 JIC</t>
         </is>
       </c>
-      <c r="BM21" t="inlineStr">
+      <c r="BM22" t="inlineStr">
         <is>
           <t>6802</t>
         </is>
       </c>
-      <c r="BN21" t="inlineStr">
+      <c r="BN22" t="inlineStr">
         <is>
           <t>2 1/2-12 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BO21" t="inlineStr">
+      <c r="BO22" t="inlineStr">
         <is>
           <t>2 1/2-12 JIC</t>
         </is>
       </c>
-      <c r="BP21" t="inlineStr">
+      <c r="BP22" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BQ21" t="inlineStr">
+      <c r="BQ22" t="inlineStr">
         <is>
           <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6802-32-32-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-02 (batch 15): the dimension cells MEASURED on the part's own Brennan STEP 09_STEP_FILES/BRENNAN_6802-32-32-NWO-FG.stp (sha256 a51a35580cb9..., received 2026-10-02, tools/_out/step_ingest_20261002/MANIFEST_sha256.txt) with tools/measure/nwo.py (the adjustable-ORB walk / parse of 2026-09-25) for the ORB end and the fix2702 measure_bh reading for the JIC leg and the bores (tools/_out/batch15_20261002/work/FG-STEP/scripts/measure_6802.py; method validated first: (A) the Brennan 6801-32-32-NWO-FG STEP turned to put its ORB leg at 45 deg returns its review row exactly; (B) OCP rebuilds (tools/measure/nwo_model.py, e45) of the accepted 6802-08-08 / -20-20 / -24-24-NWO-FG turned into the Brennan layout return their generated values exactly; work/FG-STEP/measure/measure_6802.txt): LEG_JIC 2.220 (crossing to the JIC tip), LEG_ORB 1.860 (crossing to the ORB tip), ORB_I3 1.140 (ORB tip to the body face), ORB_THDL 0.469 (ORB thread length, tip to the undercut), ORB_GRVDIA 2.381 (undercut root dia), HEXB 2.750 (locknut across flats), Y 2.500 (body hex flats), D1 1.781 (JIC bore), D2 1.781 (ORB bore); THDMAJ_A 2.5 / THDMAJ_B 2.5 = the -32 JIC / -32 ORB dash of the part number (STEP thread majors 2.5 / 2.5; OMi Items row 2239 Side 1 / 2 Thread); JIC_RELIEFL / RELIEFANG / JIC_THDZ / JIC_CONEDIA / JIC_LANDL / JIC_SEATL / SEATB = the -32 MS33656J chain of the generator JIC library (gen_straight2.JIC[32], 2403 table VERIFIED vs Brennan) = every -32 JIC row of this table (gen_tee builds the JIC end from that library) [standing user decision: a forged -FG part may be built from its own Brennan STEP; one manufacturer -&gt; ASSUMED]. The Brennan forging stops its corner at the ORB body face (0.720; past it only the neck r 1.25 up to the locknut at 0.747, work/FG-STEP/measure/corner_scan_6802-32-32.txt) - as the corner neck trim ORBTRIM assumes. The adjustable ORB end of this STEP (locknut 0.41 thick, washer 1.58 x 0.05, undercut 0.184 long, thread 0.469, undercut root 2.381, I3 1.14) = gen_tee NWO_MEAS[-32] (Brennan 6801-32-32-NWO-FG) EXCEPT the neck: r 1.25 (flush with the body hex flats) x 0.027 here, r 1.10 x 0.027 in NWO_MEAS[-32] = the model (see $COMMENT). ORB_GRVW left EMPTY (no source): Parker ORD-5700 Table 4-4 prints no groove width G on the -32 row (07_RAW_EXTRACTS/Report_ORB_groove_ORD5700.md: G not printed for 3-914..3-932), the table title lists "ORB -14/-32 groove width" as a remaining block, and no -32 ORB row of this table carries one - the accepted 6801-32-32-NWO-FG row is empty for the same reason ($COMMENT "ORB -32 groove width UNPUBLISHED and unmeasured"). The only -32 value on file, 0.125 in gen_straight2.ORB[32], was measured on a different part (the fixed-ORB Brennan 6400-32-32-O STEP); using it here would be a transfer from another part that no user decision covers. The row is still ASSUMED: gen_tee does not read ORB_GRVW and it is not in the SW2 table, so every value the model uses has a source; the empty cell keeps the groove width itself unsourced, as on the accepted -32 row. The Brennan TFA catalog p42 (table TFA-p042-t01) (page-verified; tools/_out/brennan_catalog_20261001/catalog_verified.json) prints M2 2.220 (JIC leg), M8 1.860 (ORB leg), C HEX 2.750, Y FLATS 2.500, B1 / B2 DRILL 1.781, B1 / B2 2 1/2-12 = the STEP (same manufacturer, not an independent source). The OMi dimension file gives no dimension for this SKU (07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items row 2239: threads only); Air-Way prints no row for this -FG part. Where the MODEL text below or a generator warning says Air-Way (legs, ORB_I3, locknut hex HEXB, groove / undercut dia, thread length, hex), this row uses these STEP values | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); CORNER NECK TRIM (45 deg elbow, 2026-10-01, feature ORBTRIM): the forged corner (30deg puck / angled hex arm) stands out of the adjustable ORB neck beyond the body face; it is cut back about the ORB axis to the ORB profile (neck, locknut inner face and inner 15deg chamfer, from the body face to the full nut corner) - as the turned ORB stud would leave it (Brennan 6502-12-12-FG STEP, 45 deg swivel elbow: the forged corner stops at the body face, only the neck beyond it). ASSUMPTION for the 6802 forging: no Brennan 6802 STEP measured; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BR21" t="inlineStr">
+      <c r="BR22" t="inlineStr">
         <is>
           <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6802-32-32-NWO dims are NOT assumed; confirm before modelling | 2026-10-02 (resolved, batch 15): built from its OWN Brennan STEP (09_STEP_FILES/BRENNAN_6802-32-32-NWO-FG.stp; one manufacturer -&gt; ASSUMED), not from the non-forged Air-Way 6802-32-32-NWO row; every measured cell equals the Brennan TFA catalog p42 row (same source). For the record, Air-Way 6802-32-32-NWO (non-FG, DROP row of this table) prints LEG_JIC 2.22 / LEG_ORB 1.86 / HEXB 2.75 / D 1.78 = the STEP within rounding, but ORB_I3 1.16 (STEP 1.14) and Y 2.63 (forged hex 2.500, STEP and catalog). MODEL vs this STEP (geometry, not a table cell): the Brennan neck between the body face (0.720) and the locknut (0.747) is r 1.25, flush with the hex flats; the gen_tee adjustable-ORB module draws the -32 neck at NWO_MEAS r 1.10 (Brennan 6801-32-32), i.e. the model lacks a ring r 1.10..1.25 x 0.027 long (about 0.030 in^3), and gen_tee cannot draw a neck equal to the flats radius (zero-height body face check) - flagged for the user, not changed. Uses the corner neck trim ORBTRIM proven on the 2026-10-02 TEST row; ORB -32 groove width UNPUBLISHED and unmeasured (ORB_GRVW empty, as on 6801-32-32-NWO-FG) | leg 1: CORNER NECK TRIM (ORBTRIM1): beyond the body face (0.720) the corner stands outside the ORB neck / locknut inner chamfer - angled hex arm by 0.219 (x=0.723, r 1.319), corner puck by 0.151 (x=0.720, r 1.251) - cut back to the ORB profile up to the full nut corner (0.805); the rest of the corner lies inside the ORB end; leg 1: the angled hex arm corner reaches 1.021 along this leg, past the locknut face (0.747) - cut back by the corner neck trim and inside the locknut envelope beyond (sampled check)</t>
         </is>
       </c>
-      <c r="BS21" t="inlineStr">
+      <c r="BS22" t="inlineStr">
         <is>
           <t>6802-32-32-NWO-FG</t>
         </is>
